--- a/VerveStacks_MAR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MAR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MAR_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C99C8A04-E74C-4A35-85D2-BA0F455D9799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55DF8CEC-73F6-4792-8D8C-4BE15093844B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -888,223 +888,277 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MAR_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MAR_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MAR_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_MAR_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MAR_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MAR_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w377048422-225_MAR,e_w207997682-225_MAR,e_w250862291-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w250862291-225_MAR,e_w163471767-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w143752299-400_MAR</t>
+  </si>
+  <si>
+    <t>e_w200913450-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w97706499-225_MAR,e_w131408509-225_MAR,e_w131902940-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w200913450-225_MAR,e_w97706499-225_MAR,e_w377048422-225_MAR,e_w200906153-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w131902940-225_MAR,e_w250862291-225_MAR,e_w95436126-225_MAR,e_w163471767-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w207997682-225_MAR,e_w250862291-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w131902940-225_MAR,e_w93147473-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w97706499-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w163471767-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w131902940-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w377048422-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w200913450-225_MAR,e_w377048422-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w200913450-225_MAR,e_w97706499-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w93147473-225_MAR,e_w163471767-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w377048422-225_MAR,e_w200906153-225_MAR,e_w207997682-225_MAR,e_w250862291-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w143681023-225_MAR,e_MA95-225_MAR</t>
+  </si>
+  <si>
+    <t>e_w250862291-225_MAR,e_w143752299-400_MAR</t>
+  </si>
+  <si>
     <t>e_w200906153-225_MAR,e_w207997682-225_MAR,e_w131902940-225_MAR</t>
   </si>
   <si>
-    <t>e_w377048422-225_MAR,e_w207997682-225_MAR,e_w250862291-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w250862291-225_MAR,e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w143752299-400_MAR</t>
-  </si>
-  <si>
-    <t>e_w200913450-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w250862291-225_MAR,e_w143752299-400_MAR</t>
-  </si>
-  <si>
     <t>e_w163471767-225_MAR,e_w143752299-400_MAR</t>
   </si>
   <si>
-    <t>e_w200913450-225_MAR,e_w377048422-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w200913450-225_MAR,e_w97706499-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w93147473-225_MAR,e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w131902940-225_MAR,e_w93147473-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w143681023-225_MAR,e_MA95-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w377048422-225_MAR,e_w200906153-225_MAR,e_w207997682-225_MAR,e_w250862291-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w97706499-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w97706499-225_MAR,e_w131408509-225_MAR,e_w131902940-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w200913450-225_MAR,e_w97706499-225_MAR,e_w377048422-225_MAR,e_w200906153-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w131902940-225_MAR,e_w250862291-225_MAR,e_w95436126-225_MAR,e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w207997682-225_MAR,e_w250862291-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w131902940-225_MAR</t>
-  </si>
-  <si>
-    <t>e_w377048422-225_MAR</t>
+    <t>distr_wonelc_won_MAR_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_MAR_016</t>
@@ -1125,28 +1179,22 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MAR_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>distr_wonelc_won_MAR_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MAR_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_MAR_022</t>
@@ -1191,52 +1239,46 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MAR_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MAR_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>elc_won_MAR_003</t>
+  </si>
+  <si>
+    <t>e_w250862291-225_MAR,e_w95436126-225_MAR,e_w163471767-225_MAR</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_020</t>
+  </si>
+  <si>
+    <t>e_MA95-225_MAR,e_w200913450-225_MAR</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_015</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_019</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_011</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_014</t>
+  </si>
+  <si>
+    <t>e_w377048422-225_MAR,e_w207997682-225_MAR</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_017</t>
+  </si>
+  <si>
+    <t>e_w131902940-225_MAR,e_w207997682-225_MAR</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_007</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_002</t>
+  </si>
+  <si>
+    <t>e_w95436126-225_MAR,e_w163471767-225_MAR</t>
   </si>
   <si>
     <t>elc_won_MAR_016</t>
@@ -1248,25 +1290,16 @@
     <t>elc_won_MAR_005</t>
   </si>
   <si>
-    <t>elc_won_MAR_017</t>
-  </si>
-  <si>
-    <t>e_w131902940-225_MAR,e_w207997682-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_007</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_002</t>
-  </si>
-  <si>
-    <t>e_w95436126-225_MAR,e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_014</t>
-  </si>
-  <si>
-    <t>e_w377048422-225_MAR,e_w207997682-225_MAR</t>
+    <t>elc_won_MAR_001</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_010</t>
+  </si>
+  <si>
+    <t>elc_won_MAR_021</t>
+  </si>
+  <si>
+    <t>e_w143681023-225_MAR,e_MA95-225_MAR,e_w200913450-225_MAR</t>
   </si>
   <si>
     <t>elc_won_MAR_022</t>
@@ -1296,39 +1329,6 @@
     <t>elc_won_MAR_004</t>
   </si>
   <si>
-    <t>elc_won_MAR_020</t>
-  </si>
-  <si>
-    <t>e_MA95-225_MAR,e_w200913450-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_015</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_011</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_001</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_010</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_003</t>
-  </si>
-  <si>
-    <t>e_w250862291-225_MAR,e_w95436126-225_MAR,e_w163471767-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_021</t>
-  </si>
-  <si>
-    <t>e_w143681023-225_MAR,e_MA95-225_MAR,e_w200913450-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_won_MAR_019</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_MAR_002</t>
   </si>
   <si>
@@ -1341,40 +1341,52 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_MAR_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MAR_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MAR_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MAR_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_MAR_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MAR_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_MAR_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MAR_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MAR_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MAR_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>distr_wofelc_wof_MAR_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MAR_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_MAR_003</t>
@@ -1383,18 +1395,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MAR_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MAR_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>elc_wof_MAR_002</t>
   </si>
   <si>
@@ -1404,37 +1404,37 @@
     <t>e_w97706499-225_MAR,e_w131408509-225_MAR</t>
   </si>
   <si>
+    <t>elc_wof_MAR_008</t>
+  </si>
+  <si>
+    <t>elc_wof_MAR_005</t>
+  </si>
+  <si>
+    <t>elc_wof_MAR_011</t>
+  </si>
+  <si>
+    <t>e_w131408509-225_MAR</t>
+  </si>
+  <si>
+    <t>elc_wof_MAR_007</t>
+  </si>
+  <si>
     <t>elc_wof_MAR_010</t>
   </si>
   <si>
-    <t>elc_wof_MAR_008</t>
-  </si>
-  <si>
     <t>elc_wof_MAR_006</t>
   </si>
   <si>
-    <t>elc_wof_MAR_005</t>
-  </si>
-  <si>
-    <t>elc_wof_MAR_011</t>
-  </si>
-  <si>
-    <t>e_w131408509-225_MAR</t>
-  </si>
-  <si>
-    <t>elc_wof_MAR_007</t>
+    <t>elc_wof_MAR_004</t>
+  </si>
+  <si>
+    <t>elc_wof_MAR_009</t>
+  </si>
+  <si>
+    <t>e_w93147473-225_MAR</t>
   </si>
   <si>
     <t>elc_wof_MAR_003</t>
-  </si>
-  <si>
-    <t>elc_wof_MAR_004</t>
-  </si>
-  <si>
-    <t>elc_wof_MAR_009</t>
-  </si>
-  <si>
-    <t>e_w93147473-225_MAR</t>
   </si>
   <si>
     <t>e_won_MAR_001</t>
@@ -6457,7 +6457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EA4C37-E498-4097-9D3E-0972BCE91D4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A33F5E31-27C0-4BE0-968C-EBD202A410D6}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6695,16 +6695,16 @@
         <v>253</v>
       </c>
       <c r="Y11" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="Z11" t="s">
         <v>305</v>
       </c>
       <c r="AA11">
-        <v>0.9988313109389787</v>
+        <v>0.99284185557883264</v>
       </c>
       <c r="AB11">
-        <v>21.425966118724819</v>
+        <v>131.23264772140135</v>
       </c>
       <c r="AD11" t="s">
         <v>252</v>
@@ -6734,13 +6734,13 @@
         <v>370</v>
       </c>
       <c r="AN11" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="AO11">
-        <v>0.9983474476922849</v>
+        <v>0.99854696905155493</v>
       </c>
       <c r="AP11">
-        <v>30.296792308111105</v>
+        <v>26.638900721493386</v>
       </c>
       <c r="AR11" t="s">
         <v>252</v>
@@ -6770,7 +6770,7 @@
         <v>422</v>
       </c>
       <c r="BB11" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="BC11">
         <v>0.99636808042415881</v>
@@ -6841,16 +6841,16 @@
         <v>257</v>
       </c>
       <c r="Y12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="Z12" t="s">
         <v>306</v>
       </c>
       <c r="AA12">
-        <v>0.99284185557883264</v>
+        <v>0.99637634884963755</v>
       </c>
       <c r="AB12">
-        <v>131.23264772140135</v>
+        <v>66.433604423312019</v>
       </c>
       <c r="AD12" t="s">
         <v>252</v>
@@ -6877,16 +6877,16 @@
         <v>328</v>
       </c>
       <c r="AM12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN12" t="s">
-        <v>307</v>
+        <v>373</v>
       </c>
       <c r="AO12">
-        <v>0.99649106745681171</v>
+        <v>0.99377248767319104</v>
       </c>
       <c r="AP12">
-        <v>64.330429958452939</v>
+        <v>114.17105932482994</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -6987,16 +6987,16 @@
         <v>259</v>
       </c>
       <c r="Y13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Z13" t="s">
         <v>307</v>
       </c>
       <c r="AA13">
-        <v>0.99637634884963755</v>
+        <v>0.99565161996244167</v>
       </c>
       <c r="AB13">
-        <v>66.433604423312019</v>
+        <v>79.720300688568543</v>
       </c>
       <c r="AD13" t="s">
         <v>252</v>
@@ -7023,16 +7023,16 @@
         <v>330</v>
       </c>
       <c r="AM13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN13" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="AO13">
-        <v>0.99801576609438181</v>
+        <v>0.99623262906601251</v>
       </c>
       <c r="AP13">
-        <v>36.377621602999966</v>
+        <v>69.068467123104583</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -7062,13 +7062,13 @@
         <v>425</v>
       </c>
       <c r="BB13" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="BC13">
-        <v>0.99615682308729492</v>
+        <v>0.99516655687116395</v>
       </c>
       <c r="BD13">
-        <v>70.458243399592376</v>
+        <v>88.613124028660636</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7133,16 +7133,16 @@
         <v>261</v>
       </c>
       <c r="Y14" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="Z14" t="s">
         <v>308</v>
       </c>
       <c r="AA14">
-        <v>0.99565161996244167</v>
+        <v>0.99530045594879712</v>
       </c>
       <c r="AB14">
-        <v>79.720300688568543</v>
+        <v>86.15830760538536</v>
       </c>
       <c r="AD14" t="s">
         <v>252</v>
@@ -7169,16 +7169,16 @@
         <v>332</v>
       </c>
       <c r="AM14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN14" t="s">
-        <v>374</v>
+        <v>308</v>
       </c>
       <c r="AO14">
-        <v>0.99902785535433136</v>
+        <v>0.99443115251853453</v>
       </c>
       <c r="AP14">
-        <v>17.822651837257641</v>
+        <v>102.09553716020108</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -7208,13 +7208,13 @@
         <v>426</v>
       </c>
       <c r="BB14" t="s">
-        <v>315</v>
+        <v>373</v>
       </c>
       <c r="BC14">
-        <v>0.99516655687116395</v>
+        <v>0.99594812627851037</v>
       </c>
       <c r="BD14">
-        <v>88.613124028660636</v>
+        <v>74.284351560644225</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7279,16 +7279,16 @@
         <v>263</v>
       </c>
       <c r="Y15" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="Z15" t="s">
         <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99530045594879712</v>
+        <v>0.99820827842674076</v>
       </c>
       <c r="AB15">
-        <v>86.15830760538536</v>
+        <v>32.848228843086204</v>
       </c>
       <c r="AD15" t="s">
         <v>252</v>
@@ -7315,16 +7315,16 @@
         <v>334</v>
       </c>
       <c r="AM15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN15" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="AO15">
-        <v>0.99449566932752642</v>
+        <v>0.99698778538632549</v>
       </c>
       <c r="AP15">
-        <v>100.91272899534873</v>
+        <v>55.223934584033323</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -7354,13 +7354,13 @@
         <v>427</v>
       </c>
       <c r="BB15" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="BC15">
-        <v>0.99678435356252015</v>
+        <v>0.99644580649311731</v>
       </c>
       <c r="BD15">
-        <v>58.953518020463633</v>
+        <v>65.160214292848408</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7425,16 +7425,16 @@
         <v>265</v>
       </c>
       <c r="Y16" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="Z16" t="s">
         <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.98993257224285114</v>
+        <v>0.99684486555938434</v>
       </c>
       <c r="AB16">
-        <v>184.56950888106178</v>
+        <v>57.844131411286099</v>
       </c>
       <c r="AD16" t="s">
         <v>252</v>
@@ -7461,16 +7461,16 @@
         <v>336</v>
       </c>
       <c r="AM16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO16">
-        <v>0.99861682345335079</v>
+        <v>0.99664394403728762</v>
       </c>
       <c r="AP16">
-        <v>25.358236688569452</v>
+        <v>61.527692649727854</v>
       </c>
       <c r="AR16" t="s">
         <v>252</v>
@@ -7497,16 +7497,16 @@
         <v>410</v>
       </c>
       <c r="BA16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="BB16" t="s">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="BC16">
-        <v>0.99594812627851037</v>
+        <v>0.99561679956745774</v>
       </c>
       <c r="BD16">
-        <v>74.284351560644225</v>
+        <v>80.358674596608026</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7571,16 +7571,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99775950660862522</v>
+        <v>0.99829141714368463</v>
       </c>
       <c r="AB17">
-        <v>41.075712175203783</v>
+        <v>31.324019032449339</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -7607,16 +7607,16 @@
         <v>338</v>
       </c>
       <c r="AM17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN17" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO17">
-        <v>0.99664394403728762</v>
+        <v>0.99902785535433136</v>
       </c>
       <c r="AP17">
-        <v>61.527692649727854</v>
+        <v>17.822651837257641</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -7643,16 +7643,16 @@
         <v>412</v>
       </c>
       <c r="BA17" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="BB17" t="s">
-        <v>430</v>
+        <v>316</v>
       </c>
       <c r="BC17">
-        <v>0.99644580649311731</v>
+        <v>0.99615682308729492</v>
       </c>
       <c r="BD17">
-        <v>65.160214292848408</v>
+        <v>70.458243399592376</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7717,16 +7717,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99106954811616688</v>
+        <v>0.99830171547594349</v>
       </c>
       <c r="AB18">
-        <v>163.72495120360657</v>
+        <v>31.135216274368524</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -7753,16 +7753,16 @@
         <v>340</v>
       </c>
       <c r="AM18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN18" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO18">
-        <v>0.99825957396062004</v>
+        <v>0.99449566932752642</v>
       </c>
       <c r="AP18">
-        <v>31.907810721965816</v>
+        <v>100.91272899534873</v>
       </c>
       <c r="AR18" t="s">
         <v>252</v>
@@ -7792,13 +7792,13 @@
         <v>431</v>
       </c>
       <c r="BB18" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="BC18">
-        <v>0.99561679956745774</v>
+        <v>0.99678435356252015</v>
       </c>
       <c r="BD18">
-        <v>80.358674596608026</v>
+        <v>58.953518020463633</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7863,16 +7863,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99886641562464373</v>
+        <v>0.99796658720252296</v>
       </c>
       <c r="AB19">
-        <v>20.782380214865714</v>
+        <v>37.279234620411664</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -7899,16 +7899,16 @@
         <v>342</v>
       </c>
       <c r="AM19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN19" t="s">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.99246015766616025</v>
+        <v>0.99861682345335079</v>
       </c>
       <c r="AP19">
-        <v>138.23044278706209</v>
+        <v>25.358236688569452</v>
       </c>
       <c r="AR19" t="s">
         <v>252</v>
@@ -7938,13 +7938,13 @@
         <v>432</v>
       </c>
       <c r="BB19" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="BC19">
-        <v>0.99563502654489255</v>
+        <v>0.99544325372970976</v>
       </c>
       <c r="BD19">
-        <v>80.024513343637324</v>
+        <v>83.540348288654201</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8009,16 +8009,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.9987608470866256</v>
+        <v>0.99888817525352591</v>
       </c>
       <c r="AB20">
-        <v>22.717803411863198</v>
+        <v>20.383453685358162</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -8045,16 +8045,16 @@
         <v>344</v>
       </c>
       <c r="AM20" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN20" t="s">
-        <v>383</v>
+        <v>309</v>
       </c>
       <c r="AO20">
-        <v>0.99877466208651655</v>
+        <v>0.9983474476922849</v>
       </c>
       <c r="AP20">
-        <v>22.464528413862546</v>
+        <v>30.296792308111105</v>
       </c>
       <c r="AR20" t="s">
         <v>252</v>
@@ -8084,13 +8084,13 @@
         <v>433</v>
       </c>
       <c r="BB20" t="s">
-        <v>313</v>
+        <v>434</v>
       </c>
       <c r="BC20">
-        <v>0.99544325372970976</v>
+        <v>0.99654206979754989</v>
       </c>
       <c r="BD20">
-        <v>83.540348288654201</v>
+        <v>63.395387044918706</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8155,16 +8155,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99796658720252296</v>
+        <v>0.99883717755599633</v>
       </c>
       <c r="AB21">
-        <v>37.279234620411664</v>
+        <v>21.318411473400172</v>
       </c>
       <c r="AD21" t="s">
         <v>252</v>
@@ -8191,16 +8191,16 @@
         <v>346</v>
       </c>
       <c r="AM21" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN21" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AO21">
-        <v>0.99131473371615664</v>
+        <v>0.99649106745681171</v>
       </c>
       <c r="AP21">
-        <v>159.22988187046158</v>
+        <v>64.330429958452939</v>
       </c>
       <c r="AR21" t="s">
         <v>252</v>
@@ -8227,16 +8227,16 @@
         <v>420</v>
       </c>
       <c r="BA21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="BB21" t="s">
-        <v>435</v>
+        <v>322</v>
       </c>
       <c r="BC21">
-        <v>0.99654206979754989</v>
+        <v>0.99563502654489255</v>
       </c>
       <c r="BD21">
-        <v>63.395387044918706</v>
+        <v>80.024513343637324</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8301,16 +8301,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AA22">
-        <v>0.99750012204459615</v>
+        <v>0.99890169478358004</v>
       </c>
       <c r="AB22">
-        <v>45.831095849071595</v>
+        <v>20.135595634366002</v>
       </c>
       <c r="AD22" t="s">
         <v>252</v>
@@ -8337,16 +8337,16 @@
         <v>348</v>
       </c>
       <c r="AM22" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN22" t="s">
-        <v>386</v>
+        <v>325</v>
       </c>
       <c r="AO22">
-        <v>0.99801652495164617</v>
+        <v>0.99801576609438181</v>
       </c>
       <c r="AP22">
-        <v>36.363709219821104</v>
+        <v>36.377621602999966</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Z23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AA23">
-        <v>0.99736061100092122</v>
+        <v>0.99868110290511669</v>
       </c>
       <c r="AB23">
-        <v>48.388798316444259</v>
+        <v>24.179780072859955</v>
       </c>
       <c r="AD23" t="s">
         <v>252</v>
@@ -8450,13 +8450,13 @@
         <v>387</v>
       </c>
       <c r="AN23" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO23">
-        <v>0.99425050404904347</v>
+        <v>0.99921737776751629</v>
       </c>
       <c r="AP23">
-        <v>105.40742576753664</v>
+        <v>14.348074262201635</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8521,16 +8521,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AA24">
-        <v>0.99888817525352591</v>
+        <v>0.99345711673723114</v>
       </c>
       <c r="AB24">
-        <v>20.383453685358162</v>
+        <v>119.95285981742924</v>
       </c>
       <c r="AD24" t="s">
         <v>252</v>
@@ -8560,13 +8560,13 @@
         <v>388</v>
       </c>
       <c r="AN24" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="AO24">
-        <v>0.99750073222567825</v>
+        <v>0.9889330474186343</v>
       </c>
       <c r="AP24">
-        <v>45.819909195898575</v>
+        <v>202.8941306583711</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8631,16 +8631,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="Z25" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AA25">
-        <v>0.99883717755599633</v>
+        <v>0.99106954811616688</v>
       </c>
       <c r="AB25">
-        <v>21.318411473400172</v>
+        <v>163.72495120360657</v>
       </c>
       <c r="AD25" t="s">
         <v>252</v>
@@ -8673,10 +8673,10 @@
         <v>390</v>
       </c>
       <c r="AO25">
-        <v>0.99377248767319104</v>
+        <v>0.99783925304383347</v>
       </c>
       <c r="AP25">
-        <v>114.17105932482994</v>
+        <v>39.613694196387165</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8741,16 +8741,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="Z26" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="AA26">
-        <v>0.99890169478358004</v>
+        <v>0.99886641562464373</v>
       </c>
       <c r="AB26">
-        <v>20.135595634366002</v>
+        <v>20.782380214865714</v>
       </c>
       <c r="AD26" t="s">
         <v>252</v>
@@ -8780,13 +8780,13 @@
         <v>391</v>
       </c>
       <c r="AN26" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="AO26">
-        <v>0.99623262906601251</v>
+        <v>0.99825957396062004</v>
       </c>
       <c r="AP26">
-        <v>69.068467123104583</v>
+        <v>31.907810721965816</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8851,16 +8851,16 @@
         <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Z27" t="s">
         <v>320</v>
       </c>
       <c r="AA27">
-        <v>0.99820827842674076</v>
+        <v>0.9987608470866256</v>
       </c>
       <c r="AB27">
-        <v>32.848228843086204</v>
+        <v>22.717803411863198</v>
       </c>
       <c r="AD27" t="s">
         <v>252</v>
@@ -8890,13 +8890,13 @@
         <v>392</v>
       </c>
       <c r="AN27" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="AO27">
-        <v>0.99698778538632549</v>
+        <v>0.99246015766616025</v>
       </c>
       <c r="AP27">
-        <v>55.223934584033323</v>
+        <v>138.23044278706209</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8961,16 +8961,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Z28" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="AA28">
-        <v>0.99684486555938434</v>
+        <v>0.99883652076834117</v>
       </c>
       <c r="AB28">
-        <v>57.844131411286099</v>
+        <v>21.330452580411702</v>
       </c>
       <c r="AD28" t="s">
         <v>252</v>
@@ -9000,13 +9000,13 @@
         <v>393</v>
       </c>
       <c r="AN28" t="s">
-        <v>315</v>
+        <v>394</v>
       </c>
       <c r="AO28">
-        <v>0.99921737776751629</v>
+        <v>0.99877466208651655</v>
       </c>
       <c r="AP28">
-        <v>14.348074262201635</v>
+        <v>22.464528413862546</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9071,16 +9071,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="Z29" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="AA29">
-        <v>0.99829141714368463</v>
+        <v>0.99323532149834592</v>
       </c>
       <c r="AB29">
-        <v>31.324019032449339</v>
+        <v>124.0191058636579</v>
       </c>
       <c r="AD29" t="s">
         <v>252</v>
@@ -9107,16 +9107,16 @@
         <v>362</v>
       </c>
       <c r="AM29" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN29" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="AO29">
-        <v>0.9889330474186343</v>
+        <v>0.99131473371615664</v>
       </c>
       <c r="AP29">
-        <v>202.8941306583711</v>
+        <v>159.22988187046158</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9181,16 +9181,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="Z30" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AA30">
-        <v>0.99830171547594349</v>
+        <v>0.99736061100092122</v>
       </c>
       <c r="AB30">
-        <v>31.135216274368524</v>
+        <v>48.388798316444259</v>
       </c>
       <c r="AD30" t="s">
         <v>252</v>
@@ -9217,16 +9217,16 @@
         <v>364</v>
       </c>
       <c r="AM30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN30" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO30">
-        <v>0.99854696905155493</v>
+        <v>0.99801652495164617</v>
       </c>
       <c r="AP30">
-        <v>26.638900721493386</v>
+        <v>36.363709219821104</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9291,16 +9291,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Z31" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="AA31">
-        <v>0.99883652076834117</v>
+        <v>0.99750012204459615</v>
       </c>
       <c r="AB31">
-        <v>21.330452580411702</v>
+        <v>45.831095849071595</v>
       </c>
       <c r="AD31" t="s">
         <v>252</v>
@@ -9327,16 +9327,16 @@
         <v>366</v>
       </c>
       <c r="AM31" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN31" t="s">
-        <v>398</v>
+        <v>323</v>
       </c>
       <c r="AO31">
-        <v>0.99783925304383347</v>
+        <v>0.99425050404904347</v>
       </c>
       <c r="AP31">
-        <v>39.613694196387165</v>
+        <v>105.40742576753664</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9401,16 +9401,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Z32" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="AA32">
-        <v>0.99323532149834592</v>
+        <v>0.98993257224285114</v>
       </c>
       <c r="AB32">
-        <v>124.0191058636579</v>
+        <v>184.56950888106178</v>
       </c>
       <c r="AD32" t="s">
         <v>252</v>
@@ -9440,13 +9440,13 @@
         <v>399</v>
       </c>
       <c r="AN32" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AO32">
-        <v>0.99443115251853453</v>
+        <v>0.99750073222567825</v>
       </c>
       <c r="AP32">
-        <v>102.09553716020108</v>
+        <v>45.819909195898575</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9511,16 +9511,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z33" t="s">
         <v>324</v>
       </c>
       <c r="AA33">
-        <v>0.99868110290511669</v>
+        <v>0.9988313109389787</v>
       </c>
       <c r="AB33">
-        <v>24.179780072859955</v>
+        <v>21.425966118724819</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9585,16 +9585,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="Z34" t="s">
         <v>325</v>
       </c>
       <c r="AA34">
-        <v>0.99345711673723114</v>
+        <v>0.99775950660862522</v>
       </c>
       <c r="AB34">
-        <v>119.95285981742924</v>
+        <v>41.075712175203783</v>
       </c>
     </row>
   </sheetData>
@@ -9603,7 +9603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3CE65D4-11C1-4B03-BF77-DC39F4AF61E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B24512-74B1-41E8-B466-CEC8515FAA52}">
   <dimension ref="B9:Z32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9715,7 +9715,7 @@
         <v>436</v>
       </c>
       <c r="K11" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="L11">
         <v>0.49578025251577712</v>
@@ -9783,7 +9783,7 @@
         <v>438</v>
       </c>
       <c r="K12" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L12">
         <v>0.20900164048993342</v>
@@ -9851,7 +9851,7 @@
         <v>440</v>
       </c>
       <c r="K13" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="L13">
         <v>0.22915303622374047</v>
@@ -9884,7 +9884,7 @@
         <v>484</v>
       </c>
       <c r="X13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Y13">
         <v>33.601500000000001</v>
@@ -9919,7 +9919,7 @@
         <v>442</v>
       </c>
       <c r="K14" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="L14">
         <v>3.701893480018124</v>
@@ -9952,7 +9952,7 @@
         <v>486</v>
       </c>
       <c r="X14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y14">
         <v>10.212</v>
@@ -9987,7 +9987,7 @@
         <v>444</v>
       </c>
       <c r="K15" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="L15">
         <v>4.3321240919983088</v>
@@ -10020,7 +10020,7 @@
         <v>488</v>
       </c>
       <c r="X15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Y15">
         <v>24.868500000000001</v>
@@ -10055,7 +10055,7 @@
         <v>446</v>
       </c>
       <c r="K16" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="L16">
         <v>2.9856744838009903</v>
@@ -10088,7 +10088,7 @@
         <v>490</v>
       </c>
       <c r="X16" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="Y16">
         <v>4.9470000000000001</v>
@@ -10123,7 +10123,7 @@
         <v>448</v>
       </c>
       <c r="K17" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="L17">
         <v>6.4688634516185992</v>
@@ -10156,7 +10156,7 @@
         <v>492</v>
       </c>
       <c r="X17" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Y17">
         <v>25.101749999999999</v>
@@ -10191,7 +10191,7 @@
         <v>450</v>
       </c>
       <c r="K18" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="L18">
         <v>0.7262486745051433</v>
@@ -10224,7 +10224,7 @@
         <v>494</v>
       </c>
       <c r="X18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y18">
         <v>13.63125</v>
@@ -10259,7 +10259,7 @@
         <v>452</v>
       </c>
       <c r="K19" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="L19">
         <v>21.463842982651965</v>
@@ -10292,7 +10292,7 @@
         <v>496</v>
       </c>
       <c r="X19" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y19">
         <v>12.1005</v>
@@ -10327,7 +10327,7 @@
         <v>454</v>
       </c>
       <c r="K20" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="L20">
         <v>24.306495623931166</v>
@@ -10360,7 +10360,7 @@
         <v>498</v>
       </c>
       <c r="X20" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Y20">
         <v>10.119</v>
@@ -10395,7 +10395,7 @@
         <v>456</v>
       </c>
       <c r="K21" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="L21">
         <v>4.2652357025854988</v>
@@ -10428,7 +10428,7 @@
         <v>500</v>
       </c>
       <c r="X21" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Y21">
         <v>14.282999999999999</v>
@@ -10463,7 +10463,7 @@
         <v>458</v>
       </c>
       <c r="K22" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="L22">
         <v>35.829528209869075</v>
@@ -10498,7 +10498,7 @@
         <v>460</v>
       </c>
       <c r="K23" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="L23">
         <v>42.726315600440493</v>
@@ -10533,7 +10533,7 @@
         <v>462</v>
       </c>
       <c r="K24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L24">
         <v>10.671728656322271</v>
@@ -10568,7 +10568,7 @@
         <v>464</v>
       </c>
       <c r="K25" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="L25">
         <v>20.954403892250863</v>
@@ -10603,7 +10603,7 @@
         <v>466</v>
       </c>
       <c r="K26" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="L26">
         <v>1.1344648114427969</v>
@@ -10638,7 +10638,7 @@
         <v>468</v>
       </c>
       <c r="K27" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L27">
         <v>0.81416493218538466</v>
@@ -10673,7 +10673,7 @@
         <v>470</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="L28">
         <v>2.3026650191878399</v>
@@ -10708,7 +10708,7 @@
         <v>472</v>
       </c>
       <c r="K29" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="L29">
         <v>22.884302144649318</v>
@@ -10743,7 +10743,7 @@
         <v>474</v>
       </c>
       <c r="K30" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="L30">
         <v>55.077387494496023</v>
@@ -10778,7 +10778,7 @@
         <v>476</v>
       </c>
       <c r="K31" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="L31">
         <v>16.877150468918583</v>
@@ -10813,7 +10813,7 @@
         <v>478</v>
       </c>
       <c r="K32" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="L32">
         <v>0.91544231753540395</v>
@@ -10828,7 +10828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16187C8-F5F8-449C-B03E-09704B4C35E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1917B7-F035-4172-839F-053C4BBC32AE}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
